--- a/jogos_2025-01-03.xlsx
+++ b/jogos_2025-01-03.xlsx
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,28 +1443,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
         <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T8" t="n">
         <v>2.75</v>
@@ -1476,22 +1476,22 @@
         <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X8" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
         <v>1.67</v>
@@ -1501,25 +1501,25 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '85']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['90+6']</t>
+          <t>['7', '19', '90']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45660.41666666666</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
         <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
         <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
         <v>2.75</v>
@@ -1605,22 +1605,22 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="X9" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AC9" t="n">
         <v>1.67</v>
@@ -1630,25 +1630,25 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['14', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['7', '19', '90']</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45660.41666666666</v>
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -1693,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.98</v>
+        <v>2.69</v>
       </c>
       <c r="M10" t="n">
-        <v>3.36</v>
+        <v>3.43</v>
       </c>
       <c r="N10" t="n">
-        <v>3.82</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.65</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>3.24</v>
+        <v>2.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
         <v>1.05</v>
       </c>
       <c r="W10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.36</v>
       </c>
-      <c r="X10" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC10" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['9', '54']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['90+6']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45660.58333333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>3.82</v>
       </c>
       <c r="O11" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="U11" t="n">
         <v>1.36</v>
@@ -1863,50 +1863,50 @@
         <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="AA11" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['34', '42', '76']</t>
+          <t>['9', '54']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45660.58333333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.69</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>3.43</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.44</v>
       </c>
       <c r="V12" t="n">
         <v>1.05</v>
       </c>
       <c r="W12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['34', '42', '76']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.25</v>
       </c>
-      <c r="X12" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AH12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['38']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['45+3']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45660.58333333334</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="M13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O13" t="n">
         <v>3.75</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.4</v>
-      </c>
       <c r="P13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['2', '89']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI13" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['37', '47']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45660.66666666666</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Martigues</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2209,91 +2209,91 @@
         <v>1</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="N14" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>12</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.12</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="X14" t="n">
-        <v>2.37</v>
+        <v>4.23</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.47</v>
+        <v>1.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.48</v>
+        <v>2.29</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.48</v>
+        <v>2.63</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['47', '85']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AI14" t="n">
         <v>1.14</v>
       </c>
-      <c r="AC14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['10']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['2', '89']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45660.66666666666</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.26</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.3</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['37', '47']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="AI16" t="n">
         <v>1.53</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['8', '82', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['36', '72']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45660.66666666666</v>
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.12</v>
+        <v>3.26</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.28</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="X17" t="n">
-        <v>3.25</v>
+        <v>2.67</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.88</v>
+        <v>2.39</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.82</v>
+        <v>1.51</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.59</v>
+        <v>4.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '82', '90+4']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['36', '72']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45660.66666666666</v>
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Martigues</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.18</v>
+        <v>2.22</v>
       </c>
       <c r="M18" t="n">
-        <v>6.35</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>14.27</v>
+        <v>3.16</v>
       </c>
       <c r="O18" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.63</v>
       </c>
-      <c r="Q18" t="n">
-        <v>12</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="X18" t="n">
-        <v>4.23</v>
+        <v>3.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.29</v>
+        <v>1.64</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.63</v>
+        <v>3.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['47', '85']</t>
+          <t>['7', '45+2', '50']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.2</v>
+        <v>1.57</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45660.66666666666</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
         <v>1.44</v>
@@ -2895,22 +2895,22 @@
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.89</v>
+        <v>3.59</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
         <v>1.83</v>
@@ -2925,20 +2925,20 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['7', '45+2', '50']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45660.66666666666</v>
